--- a/datos.xlsx
+++ b/datos.xlsx
@@ -3663,7 +3663,11 @@
           <t>Si</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -3351,7 +3351,11 @@
           <t>Si</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4262,6 +4262,60 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>124930.0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TIENDA MAGDALENA AV. JOSE GALVEZ N°695</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MILAGROS URBANO</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Monica Maria Damian De Los Rios</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>KÁBALA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Luz Mercedes</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>20261007-01</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4264,10 +4264,8 @@
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>124930.0</t>
-        </is>
+      <c r="B73" t="n">
+        <v>124930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4292,10 +4290,8 @@
           <t>KÁBALA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
+      <c r="H73" t="n">
+        <v>450</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4315,6 +4311,60 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>120365.0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TIENDA WONG ALDABAS SURCO AV BENAVIDES CDRA 52</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ROGGER GARCIA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yeremy Nayelly Paz Marquez</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>TINKA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>20261013-01</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
